--- a/reservation_forms/016_paragliding_experience_reservation_form--reservation_forms.xlsx
+++ b/reservation_forms/016_paragliding_experience_reservation_form--reservation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'experience',_'description':_'experience_1'}</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'experience', 'description': 'Experience 1'}</t>
+          <t>experience</t>
         </is>
       </c>
     </row>
@@ -826,29 +826,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'experience',_'description':_'experience_2'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'experience', 'description': 'Experience 2'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>provider_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'experience',_'description':_'experience_3'}</t>
+          <t>provider_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'experience', 'description': 'Experience 3'}</t>
+          <t>Provider 1</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'provider_1'}</t>
+          <t>provider_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Provider 1'}</t>
+          <t>Provider 2</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'provider_2'}</t>
+          <t>provider_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Provider 2'}</t>
+          <t>Provider 3</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'provider_3'}</t>
+          <t>provider_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Provider 3'}</t>
+          <t>Provider 4</t>
         </is>
       </c>
     </row>
@@ -911,29 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'provider_4'}</t>
+          <t>provider_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Provider 4'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>provider_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'name':_'provider_5'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'name': 'Provider 5'}</t>
+          <t>Provider 5</t>
         </is>
       </c>
     </row>
